--- a/CardData/Weapon.xlsx
+++ b/CardData/Weapon.xlsx
@@ -80,7 +80,7 @@
     <t>1|2|1|1</t>
   </si>
   <si>
-    <t>1|4|4|2</t>
+    <t>2|4|4|2</t>
   </si>
 </sst>
 </file>
